--- a/artfynd/A 27100-2025 artfynd.xlsx
+++ b/artfynd/A 27100-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,115 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126131002</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57755</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Neder Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>421799</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6962920</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27100-2025 artfynd.xlsx
+++ b/artfynd/A 27100-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>126131002</v>
       </c>
       <c r="B3" t="n">
-        <v>57755</v>
+        <v>57756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27100-2025 artfynd.xlsx
+++ b/artfynd/A 27100-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,7 +804,7 @@
         <v>126131002</v>
       </c>
       <c r="B3" t="n">
-        <v>57756</v>
+        <v>57760</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,6 +907,3469 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126348570</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>421718</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6962934</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126348573</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>421710</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6962943</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126348577</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>421772</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6963018</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126348572</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>421708</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6962945</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126348575</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>421764</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6962985</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126348549</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>421850</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6962901</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126348545</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>421798</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6962918</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126348563</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>421940</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6962807</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126348564</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>421951</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6962808</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126348555</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>421914</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6962895</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126348559</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>421941</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6962845</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126348551</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>421872</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6962886</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre på två träd</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126348558</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>421929</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6962866</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126348566</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>421893</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6962815</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126348547</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>421831</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6962917</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126348543</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>421884</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6962920</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126348546</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>421810</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6962915</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126348550</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>421850</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6962898</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126348574</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>421781</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6962972</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126348553</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>421877</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6962879</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126348578</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>421783</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6962996</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre på två träd</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126348557</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>421931</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6962875</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126348568</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>421710</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6962933</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126348554</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>421880</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6962878</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126348565</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>421894</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6962782</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126348560</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>421948</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6962838</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126348548</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>421844</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6962882</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126348552</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>421875</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6962871</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126348571</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>421698</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6962957</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126348567</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>421861</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6962845</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126348581</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>421959</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6962773</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126348562</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>421933</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6962808</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126348556</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>421910</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6962879</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126348576</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>421730</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6963036</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27100-2025 artfynd.xlsx
+++ b/artfynd/A 27100-2025 artfynd.xlsx
@@ -3256,7 +3256,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126348554</v>
+        <v>126348565</v>
       </c>
       <c r="B27" t="n">
         <v>57656</v>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421880</v>
+        <v>421894</v>
       </c>
       <c r="R27" t="n">
-        <v>6962878</v>
+        <v>6962782</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126348565</v>
+        <v>126348554</v>
       </c>
       <c r="B28" t="n">
         <v>57656</v>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421894</v>
+        <v>421880</v>
       </c>
       <c r="R28" t="n">
-        <v>6962782</v>
+        <v>6962878</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 27100-2025 artfynd.xlsx
+++ b/artfynd/A 27100-2025 artfynd.xlsx
@@ -3868,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126348567</v>
+        <v>126348581</v>
       </c>
       <c r="B33" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>421861</v>
+        <v>421959</v>
       </c>
       <c r="R33" t="n">
-        <v>6962845</v>
+        <v>6962773</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,11 +3939,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3970,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126348581</v>
+        <v>126348567</v>
       </c>
       <c r="B34" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3981,21 +3976,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4000,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421959</v>
+        <v>421861</v>
       </c>
       <c r="R34" t="n">
-        <v>6962773</v>
+        <v>6962845</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,6 +4036,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 27100-2025 artfynd.xlsx
+++ b/artfynd/A 27100-2025 artfynd.xlsx
@@ -3256,7 +3256,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126348565</v>
+        <v>126348554</v>
       </c>
       <c r="B27" t="n">
         <v>57656</v>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421894</v>
+        <v>421880</v>
       </c>
       <c r="R27" t="n">
-        <v>6962782</v>
+        <v>6962878</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126348554</v>
+        <v>126348565</v>
       </c>
       <c r="B28" t="n">
         <v>57656</v>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421880</v>
+        <v>421894</v>
       </c>
       <c r="R28" t="n">
-        <v>6962878</v>
+        <v>6962782</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 27100-2025 artfynd.xlsx
+++ b/artfynd/A 27100-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>126131002</v>
       </c>
       <c r="B3" t="n">
-        <v>57760</v>
+        <v>57761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>126348570</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>126348573</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>126348577</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>126348572</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>126348575</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>126348549</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>126348545</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>126348563</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>126348564</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>126348555</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>126348559</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>126348551</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>126348558</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>126348566</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>126348547</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>126348543</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>126348546</v>
       </c>
       <c r="B20" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>126348550</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>126348574</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>126348553</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>126348578</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>126348557</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>126348568</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>126348554</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>126348565</v>
       </c>
       <c r="B28" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>126348560</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>126348548</v>
       </c>
       <c r="B30" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>126348552</v>
       </c>
       <c r="B31" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>126348571</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126348581</v>
+        <v>126348567</v>
       </c>
       <c r="B33" t="n">
-        <v>91260</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>421959</v>
+        <v>421861</v>
       </c>
       <c r="R33" t="n">
-        <v>6962773</v>
+        <v>6962845</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,6 +3939,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3965,10 +3970,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126348567</v>
+        <v>126348581</v>
       </c>
       <c r="B34" t="n">
-        <v>57656</v>
+        <v>91263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,21 +3981,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4000,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421861</v>
+        <v>421959</v>
       </c>
       <c r="R34" t="n">
-        <v>6962845</v>
+        <v>6962773</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,11 +4041,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,7 +4070,7 @@
         <v>126348562</v>
       </c>
       <c r="B35" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>126348556</v>
       </c>
       <c r="B36" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>126348576</v>
       </c>
       <c r="B37" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 27100-2025 artfynd.xlsx
+++ b/artfynd/A 27100-2025 artfynd.xlsx
@@ -3868,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126348567</v>
+        <v>126348581</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>421861</v>
+        <v>421959</v>
       </c>
       <c r="R33" t="n">
-        <v>6962845</v>
+        <v>6962773</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,11 +3939,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3970,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126348581</v>
+        <v>126348567</v>
       </c>
       <c r="B34" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3981,21 +3976,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4000,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421959</v>
+        <v>421861</v>
       </c>
       <c r="R34" t="n">
-        <v>6962773</v>
+        <v>6962845</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,6 +4036,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 27100-2025 artfynd.xlsx
+++ b/artfynd/A 27100-2025 artfynd.xlsx
@@ -3868,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126348581</v>
+        <v>126348567</v>
       </c>
       <c r="B33" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>421959</v>
+        <v>421861</v>
       </c>
       <c r="R33" t="n">
-        <v>6962773</v>
+        <v>6962845</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,6 +3939,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3965,10 +3970,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126348567</v>
+        <v>126348581</v>
       </c>
       <c r="B34" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,21 +3981,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4000,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421861</v>
+        <v>421959</v>
       </c>
       <c r="R34" t="n">
-        <v>6962845</v>
+        <v>6962773</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,11 +4041,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 27100-2025 artfynd.xlsx
+++ b/artfynd/A 27100-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>51232812</v>
       </c>
       <c r="B2" t="n">
-        <v>56278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421865.5766540952</v>
+        <v>421866</v>
       </c>
       <c r="R2" t="n">
-        <v>6962976.355958289</v>
+        <v>6962976</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -801,27 +796,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126131002</v>
+        <v>126348543</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -829,32 +824,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Neder Dammtjärnen, Hjd</t>
+          <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421799</v>
+        <v>421884</v>
       </c>
       <c r="R3" t="n">
         <v>6962920</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,12 +861,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,22 +886,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126348570</v>
+        <v>126348545</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421718</v>
+        <v>421798</v>
       </c>
       <c r="R4" t="n">
-        <v>6962934</v>
+        <v>6962918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126348573</v>
+        <v>126348546</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421710</v>
+        <v>421810</v>
       </c>
       <c r="R5" t="n">
-        <v>6962943</v>
+        <v>6962915</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348577</v>
+        <v>126348547</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421772</v>
+        <v>421831</v>
       </c>
       <c r="R6" t="n">
-        <v>6963018</v>
+        <v>6962917</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1177,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348572</v>
+        <v>126348548</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421708</v>
+        <v>421844</v>
       </c>
       <c r="R7" t="n">
-        <v>6962945</v>
+        <v>6962882</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,7 +1279,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348575</v>
+        <v>126348549</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421764</v>
+        <v>421850</v>
       </c>
       <c r="R8" t="n">
-        <v>6962985</v>
+        <v>6962901</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1381,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348549</v>
+        <v>126348550</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1446,7 @@
         <v>421850</v>
       </c>
       <c r="R9" t="n">
-        <v>6962901</v>
+        <v>6962898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348545</v>
+        <v>126348551</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421798</v>
+        <v>421872</v>
       </c>
       <c r="R10" t="n">
-        <v>6962918</v>
+        <v>6962886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,7 +1585,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre på två träd</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126348563</v>
+        <v>126348552</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421940</v>
+        <v>421875</v>
       </c>
       <c r="R11" t="n">
-        <v>6962807</v>
+        <v>6962871</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126348564</v>
+        <v>126348553</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421951</v>
+        <v>421877</v>
       </c>
       <c r="R12" t="n">
-        <v>6962808</v>
+        <v>6962879</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,7 +1789,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126348555</v>
+        <v>126348554</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421914</v>
+        <v>421880</v>
       </c>
       <c r="R13" t="n">
-        <v>6962895</v>
+        <v>6962878</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,10 +1918,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126348559</v>
+        <v>126348555</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421941</v>
+        <v>421914</v>
       </c>
       <c r="R14" t="n">
-        <v>6962845</v>
+        <v>6962895</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2032,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126348551</v>
+        <v>126348556</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421872</v>
+        <v>421910</v>
       </c>
       <c r="R15" t="n">
-        <v>6962886</v>
+        <v>6962879</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,7 +2095,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre på två träd</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2134,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126348558</v>
+        <v>126348557</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421929</v>
+        <v>421931</v>
       </c>
       <c r="R16" t="n">
-        <v>6962866</v>
+        <v>6962875</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2236,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126348566</v>
+        <v>126348558</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421893</v>
+        <v>421929</v>
       </c>
       <c r="R17" t="n">
-        <v>6962815</v>
+        <v>6962866</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,7 +2299,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2338,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126348547</v>
+        <v>126348559</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421831</v>
+        <v>421941</v>
       </c>
       <c r="R18" t="n">
-        <v>6962917</v>
+        <v>6962845</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,7 +2401,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2440,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126348543</v>
+        <v>126348560</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421884</v>
+        <v>421948</v>
       </c>
       <c r="R19" t="n">
-        <v>6962920</v>
+        <v>6962838</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,7 +2503,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2542,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126348546</v>
+        <v>126348562</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421810</v>
+        <v>421933</v>
       </c>
       <c r="R20" t="n">
-        <v>6962915</v>
+        <v>6962808</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2644,10 +2632,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126348550</v>
+        <v>126348563</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421850</v>
+        <v>421940</v>
       </c>
       <c r="R21" t="n">
-        <v>6962898</v>
+        <v>6962807</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2746,10 +2734,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126348574</v>
+        <v>126348564</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,10 +2769,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421781</v>
+        <v>421951</v>
       </c>
       <c r="R22" t="n">
-        <v>6962972</v>
+        <v>6962808</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2848,10 +2836,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126348553</v>
+        <v>126348565</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,10 +2871,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421877</v>
+        <v>421894</v>
       </c>
       <c r="R23" t="n">
-        <v>6962879</v>
+        <v>6962782</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,7 +2911,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2950,10 +2938,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126348578</v>
+        <v>126348566</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2985,10 +2973,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421783</v>
+        <v>421893</v>
       </c>
       <c r="R24" t="n">
-        <v>6962996</v>
+        <v>6962815</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3025,7 +3013,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre på två träd</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3052,10 +3040,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126348557</v>
+        <v>126348567</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3087,10 +3075,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421931</v>
+        <v>421861</v>
       </c>
       <c r="R25" t="n">
-        <v>6962875</v>
+        <v>6962845</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,7 +3115,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3157,7 +3145,7 @@
         <v>126348568</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3256,10 +3244,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126348554</v>
+        <v>126348570</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,10 +3279,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421880</v>
+        <v>421718</v>
       </c>
       <c r="R27" t="n">
-        <v>6962878</v>
+        <v>6962934</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3331,7 +3319,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3358,10 +3346,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126348565</v>
+        <v>126348571</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3393,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421894</v>
+        <v>421698</v>
       </c>
       <c r="R28" t="n">
-        <v>6962782</v>
+        <v>6962957</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3433,7 +3421,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3460,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126348560</v>
+        <v>126348572</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3495,10 +3483,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421948</v>
+        <v>421708</v>
       </c>
       <c r="R29" t="n">
-        <v>6962838</v>
+        <v>6962945</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,7 +3523,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3562,10 +3550,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126348548</v>
+        <v>126348573</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3597,10 +3585,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421844</v>
+        <v>421710</v>
       </c>
       <c r="R30" t="n">
-        <v>6962882</v>
+        <v>6962943</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3664,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126348552</v>
+        <v>126348574</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421875</v>
+        <v>421781</v>
       </c>
       <c r="R31" t="n">
-        <v>6962871</v>
+        <v>6962972</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3739,7 +3727,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3766,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126348571</v>
+        <v>126348575</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>421698</v>
+        <v>421764</v>
       </c>
       <c r="R32" t="n">
-        <v>6962957</v>
+        <v>6962985</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3841,7 +3829,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3868,10 +3856,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126348567</v>
+        <v>126348576</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,10 +3891,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>421861</v>
+        <v>421730</v>
       </c>
       <c r="R33" t="n">
-        <v>6962845</v>
+        <v>6963036</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3943,7 +3931,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3970,10 +3958,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126348581</v>
+        <v>126348577</v>
       </c>
       <c r="B34" t="n">
-        <v>91263</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3981,21 +3969,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +3993,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>421959</v>
+        <v>421772</v>
       </c>
       <c r="R34" t="n">
-        <v>6962773</v>
+        <v>6963018</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,6 +4029,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4067,10 +4060,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126348562</v>
+        <v>126348578</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4102,10 +4095,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>421933</v>
+        <v>421783</v>
       </c>
       <c r="R35" t="n">
-        <v>6962808</v>
+        <v>6962996</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4142,7 +4135,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre på två träd</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4169,10 +4162,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126348556</v>
+        <v>126131002</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>58057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4180,16 +4173,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4197,20 +4190,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Neder Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>421910</v>
+        <v>421799</v>
       </c>
       <c r="R36" t="n">
-        <v>6962879</v>
+        <v>6962920</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4234,17 +4239,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4259,117 +4259,15 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>126348576</v>
-      </c>
-      <c r="B37" t="n">
-        <v>57657</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Råberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>421730</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6963036</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27100-2025 artfynd.xlsx
+++ b/artfynd/A 27100-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/51232812</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348543</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348545</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348546</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348547</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348548</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348549</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348551</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1711,6 +1761,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348552</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1813,6 +1868,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348553</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1915,6 +1975,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348554</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348555</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348556</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2221,6 +2296,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348557</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2323,6 +2403,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348558</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2425,6 +2510,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348559</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2527,6 +2617,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348560</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2629,6 +2724,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348562</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2731,6 +2831,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348563</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2833,6 +2938,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348564</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2935,6 +3045,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348565</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3037,6 +3152,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348566</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3139,6 +3259,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348567</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3241,6 +3366,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348568</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3343,6 +3473,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348570</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3445,6 +3580,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348571</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3547,6 +3687,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348572</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3649,6 +3794,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348573</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3751,6 +3901,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348574</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3853,6 +4008,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348575</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3955,6 +4115,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348576</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4057,6 +4222,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348577</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4159,6 +4329,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348578</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4268,8 +4443,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126131002</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>